--- a/artfynd/A 18922-2025 artfynd.xlsx
+++ b/artfynd/A 18922-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>115116958</v>
       </c>
       <c r="B2" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,16 +779,11 @@
         <v>115116948</v>
       </c>
       <c r="B3" t="n">
-        <v>90774</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -806,12 +796,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -890,12 +880,7 @@
         <v>115116964</v>
       </c>
       <c r="B4" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,6 +976,201 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122940649</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skybygget, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>565105</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6514032</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>80038438</v>
+      </c>
+      <c r="B6" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gubbens täppa, Rodga, Norrköpings kommun, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>565090</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6514088</v>
+      </c>
+      <c r="S6" t="n">
+        <v>24</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-09-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Axel Lindahl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Axel Lindahl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18922-2025 artfynd.xlsx
+++ b/artfynd/A 18922-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115116958</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115116948</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115116964</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122940649</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,8 +1195,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80038438</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>